--- a/25-end_Testing_links_incentivai copy.xlsx
+++ b/25-end_Testing_links_incentivai copy.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gio/github/IncentivAI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4286ED-1D4C-E847-A9E2-4BB1C7FC2DAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BACCFE-C611-5541-A329-C822DC466588}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17980" xr2:uid="{695C1AA0-4E41-4E17-8F12-C07DD2378673}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{695C1AA0-4E41-4E17-8F12-C07DD2378673}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,24 +36,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
   <si>
     <t>URLs</t>
-  </si>
-  <si>
-    <t>http://deq.mt.gov/Energy/PropertyTaxIncentives.mcpx</t>
-  </si>
-  <si>
-    <t>http://development.ohio.gov/bs/bs_renewenergy.htm</t>
-  </si>
-  <si>
-    <t>http://dor.mo.gov/business/sales/taxholiday/green/</t>
-  </si>
-  <si>
-    <t>http://dor.wa.gov/content/findtaxesandrates/bandotax</t>
-  </si>
-  <si>
-    <t>http://dor.wa.gov/Content/FindTaxesAndRates/TaxIncentives/IncentivePrograms.aspx#Energy</t>
   </si>
   <si>
     <t>http://energy.gov/lpo/loan-programs-office</t>
@@ -270,19 +255,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="&quot;Aptos Narrow&quot;"/>
     </font>
   </fonts>
   <fills count="2">
@@ -305,9 +284,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -642,440 +620,382 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BFA5405-D73C-4729-8263-C7140667B5A8}">
-  <dimension ref="A1:A102"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <dimension ref="A1:A75"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="1"/>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1"/>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1"/>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1"/>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1"/>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1"/>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="1"/>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1"/>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="1"/>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1"/>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="1"/>
-    </row>
-    <row r="24" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="62" spans="1:1">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="63" spans="1:1">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="64" spans="1:1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="71" spans="1:1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="72" spans="1:1">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="73" spans="1:1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="74" spans="1:1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="75" spans="1:1">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="78" spans="1:1">
-      <c r="A78" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="79" spans="1:1">
-      <c r="A79" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="83" spans="1:1">
-      <c r="A83" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="84" spans="1:1">
-      <c r="A84" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:1">
-      <c r="A86" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="87" spans="1:1">
-      <c r="A87" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="88" spans="1:1">
-      <c r="A88" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:1">
-      <c r="A89" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" t="s">
         <v>70</v>
-      </c>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="101" spans="1:1">
-      <c r="A101" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="102" spans="1:1">
-      <c r="A102" t="s">
-        <v>75</v>
       </c>
     </row>
   </sheetData>
